--- a/main/StructureDefinition-bc-role-relationships.xlsx
+++ b/main/StructureDefinition-bc-role-relationships.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T21:39:06+00:00</t>
+    <t>2026-04-01T23:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -781,7 +781,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -2873,7 +2873,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>166</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>171</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>201</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>212</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>218</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>267</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>276</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>289</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>300</v>
       </c>
@@ -7901,12 +7901,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN55">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
